--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007135</v>
+        <v>125007127</v>
       </c>
       <c r="B4" t="n">
         <v>98018</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749115</v>
+        <v>748997</v>
       </c>
       <c r="R4" t="n">
-        <v>7192847</v>
+        <v>7192811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007127</v>
+        <v>125007031</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748997</v>
+        <v>748931</v>
       </c>
       <c r="R5" t="n">
-        <v>7192811</v>
+        <v>7192786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007031</v>
+        <v>125007135</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1108,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748931</v>
+        <v>749115</v>
       </c>
       <c r="R6" t="n">
-        <v>7192786</v>
+        <v>7192847</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007127</v>
+        <v>125007032</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748997</v>
+        <v>749096</v>
       </c>
       <c r="R4" t="n">
-        <v>7192811</v>
+        <v>7192865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007031</v>
+        <v>125007135</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748931</v>
+        <v>749115</v>
       </c>
       <c r="R5" t="n">
-        <v>7192786</v>
+        <v>7192847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007135</v>
+        <v>125007127</v>
       </c>
       <c r="B6" t="n">
         <v>98018</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749115</v>
+        <v>748997</v>
       </c>
       <c r="R6" t="n">
-        <v>7192847</v>
+        <v>7192811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007032</v>
+        <v>125007031</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>749096</v>
+        <v>748931</v>
       </c>
       <c r="R7" t="n">
-        <v>7192865</v>
+        <v>7192786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007032</v>
+        <v>125007135</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749096</v>
+        <v>749115</v>
       </c>
       <c r="R4" t="n">
-        <v>7192865</v>
+        <v>7192847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007135</v>
+        <v>125007032</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749115</v>
+        <v>749096</v>
       </c>
       <c r="R5" t="n">
-        <v>7192847</v>
+        <v>7192865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007127</v>
+        <v>125007031</v>
       </c>
       <c r="B6" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1108,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748997</v>
+        <v>748931</v>
       </c>
       <c r="R6" t="n">
-        <v>7192811</v>
+        <v>7192786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007031</v>
+        <v>125007127</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748931</v>
+        <v>748997</v>
       </c>
       <c r="R7" t="n">
-        <v>7192786</v>
+        <v>7192811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007135</v>
+        <v>125007031</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749115</v>
+        <v>748931</v>
       </c>
       <c r="R4" t="n">
-        <v>7192847</v>
+        <v>7192786</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007032</v>
+        <v>125007135</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749096</v>
+        <v>749115</v>
       </c>
       <c r="R5" t="n">
-        <v>7192865</v>
+        <v>7192847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007031</v>
+        <v>125007032</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748931</v>
+        <v>749096</v>
       </c>
       <c r="R6" t="n">
-        <v>7192786</v>
+        <v>7192865</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007031</v>
+        <v>125007135</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748931</v>
+        <v>749115</v>
       </c>
       <c r="R4" t="n">
-        <v>7192786</v>
+        <v>7192847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007135</v>
+        <v>125007127</v>
       </c>
       <c r="B5" t="n">
         <v>98018</v>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749115</v>
+        <v>748997</v>
       </c>
       <c r="R5" t="n">
-        <v>7192847</v>
+        <v>7192811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007032</v>
+        <v>125007031</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749096</v>
+        <v>748931</v>
       </c>
       <c r="R6" t="n">
-        <v>7192865</v>
+        <v>7192786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007127</v>
+        <v>125007032</v>
       </c>
       <c r="B7" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748997</v>
+        <v>749096</v>
       </c>
       <c r="R7" t="n">
-        <v>7192811</v>
+        <v>7192865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007135</v>
+        <v>125007032</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749115</v>
+        <v>749096</v>
       </c>
       <c r="R4" t="n">
-        <v>7192847</v>
+        <v>7192865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007127</v>
+        <v>125007135</v>
       </c>
       <c r="B5" t="n">
         <v>98018</v>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748997</v>
+        <v>749115</v>
       </c>
       <c r="R5" t="n">
-        <v>7192811</v>
+        <v>7192847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007032</v>
+        <v>125007127</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>749096</v>
+        <v>748997</v>
       </c>
       <c r="R7" t="n">
-        <v>7192865</v>
+        <v>7192811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007032</v>
+        <v>125007135</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749096</v>
+        <v>749115</v>
       </c>
       <c r="R4" t="n">
-        <v>7192865</v>
+        <v>7192847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007135</v>
+        <v>125007127</v>
       </c>
       <c r="B5" t="n">
         <v>98018</v>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749115</v>
+        <v>748997</v>
       </c>
       <c r="R5" t="n">
-        <v>7192847</v>
+        <v>7192811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007031</v>
+        <v>125007032</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748931</v>
+        <v>749096</v>
       </c>
       <c r="R6" t="n">
-        <v>7192786</v>
+        <v>7192865</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007127</v>
+        <v>125007031</v>
       </c>
       <c r="B7" t="n">
-        <v>98018</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748997</v>
+        <v>748931</v>
       </c>
       <c r="R7" t="n">
-        <v>7192811</v>
+        <v>7192786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>125007135</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>98186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>125007127</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>98186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>125007032</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>125007031</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -892,37 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007135</v>
+        <v>125007032</v>
       </c>
       <c r="B4" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749115</v>
+        <v>749096</v>
       </c>
       <c r="R4" t="n">
-        <v>7192847</v>
+        <v>7192865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,16 +989,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007127</v>
+        <v>125007135</v>
       </c>
       <c r="B5" t="n">
         <v>98186</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1034,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748997</v>
+        <v>749115</v>
       </c>
       <c r="R5" t="n">
-        <v>7192811</v>
+        <v>7192847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,16 +1086,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007032</v>
+        <v>125007031</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1136,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749096</v>
+        <v>748931</v>
       </c>
       <c r="R6" t="n">
-        <v>7192865</v>
+        <v>7192786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,37 +1183,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007031</v>
+        <v>125007127</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748931</v>
+        <v>748997</v>
       </c>
       <c r="R7" t="n">
-        <v>7192786</v>
+        <v>7192811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356692</v>
+        <v>113356690</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749128</v>
+        <v>749233</v>
       </c>
       <c r="R2" t="n">
-        <v>7192837</v>
+        <v>7192834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,55 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120858426</v>
+        <v>113356691</v>
       </c>
       <c r="B3" t="n">
-        <v>56245</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnfors, Vb</t>
+          <t>Boliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749218</v>
+        <v>748974</v>
       </c>
       <c r="R3" t="n">
-        <v>7192828</v>
+        <v>7192842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,30 +861,30 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Simon Bystedt</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Sweco naturvärdesinventering och artinventering</t>
+          <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007032</v>
+        <v>113356692</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -923,14 +908,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ö Fått, Vb</t>
+          <t>Boliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749096</v>
+        <v>749128</v>
       </c>
       <c r="R4" t="n">
-        <v>7192865</v>
+        <v>7192837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,44 +962,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Eriksson</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Eriksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007135</v>
+        <v>125007031</v>
       </c>
       <c r="B5" t="n">
-        <v>98186</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749115</v>
+        <v>748931</v>
       </c>
       <c r="R5" t="n">
-        <v>7192847</v>
+        <v>7192786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,14 +1075,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007031</v>
+        <v>125007032</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1121,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748931</v>
+        <v>749096</v>
       </c>
       <c r="R6" t="n">
-        <v>7192786</v>
+        <v>7192865</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007127</v>
+        <v>113441411</v>
       </c>
       <c r="B7" t="n">
-        <v>98186</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ö Fått, Vb</t>
+          <t>Västerbottens län, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748997</v>
+        <v>749191</v>
       </c>
       <c r="R7" t="n">
-        <v>7192811</v>
+        <v>7192844</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,12 +1237,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,15 +1262,416 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120858426</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>749218</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7192828</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Simon Bystedt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125007127</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>748997</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7192811</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Elin Eriksson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Elin Eriksson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125007135</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>749115</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7192847</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113356614</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Boliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>749058</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7192850</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23725-2025 artfynd.xlsx
+++ b/artfynd/A 23725-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356692</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441411</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120858426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007135</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,8 +1722,25 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>